--- a/uat_irt/UAT_IRT_RTSM_Workbook.xlsx
+++ b/uat_irt/UAT_IRT_RTSM_Workbook.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">IRT / RTSM User Acceptance Testing  —  how to run this UAT (parallel-group study)</t>
   </si>
   <si>
-    <t xml:space="preserve">UAT is your confirmation, in a TEST environment, that the vendor's randomization &amp; drug-supply build does exactly what the URS says — before a single real participant is randomized. This workbook is the tool you fill in as you go; the HTML 'UAT guide' walks the full detail with worked test scripts. As the biostatistician you OWN the confirmation that the IRT allocates per your list: right arm, right stratum, right block behaviour, concealed until dosing.</t>
+    <t xml:space="preserve">UAT is your confirmation, in a TEST environment, that the vendor's randomization &amp; drug-supply build does exactly what the URS says — before a single real participant is randomized. This workbook is the tool you fill in as you go; the HTML 'UAT guide' walks the full detail with worked test scripts. As the biostatistician you OWN the confirmation that the IRT allocates per your list: right arm, right stratum, right block behavior, concealed until dosing.</t>
   </si>
   <si>
     <t xml:space="preserve">The five sheets, in order of use</t>
@@ -486,7 +486,7 @@
     <t xml:space="preserve">URS-DSP-05</t>
   </si>
   <si>
-    <t xml:space="preserve">Blinded kit labelling</t>
+    <t xml:space="preserve">Blinded kit labeling</t>
   </si>
   <si>
     <t xml:space="preserve">Inspect kit label as a blinded role.</t>
